--- a/data/payers.xlsx
+++ b/data/payers.xlsx
@@ -1,204 +1,221 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25330"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alish dahal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0889E83-D11D-4961-ADD8-33F3B0F54967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF57794-B0DD-41A6-A891-AB5EF37AAE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Payer_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
-  <si>
-    <t>Payer_Name</t>
-  </si>
-  <si>
-    <t>Payer_Type</t>
-  </si>
-  <si>
-    <t>Coverage_Area</t>
-  </si>
-  <si>
-    <t>Plan_Types</t>
-  </si>
-  <si>
-    <t>Eligibility_Check</t>
-  </si>
-  <si>
-    <t>Claim_Submission</t>
-  </si>
-  <si>
-    <t>Data_Flow</t>
-  </si>
-  <si>
-    <t>Processing</t>
-  </si>
-  <si>
-    <t>Turnaround_Time</t>
-  </si>
-  <si>
-    <t>Payment</t>
-  </si>
-  <si>
-    <t>Denial_Reasons</t>
-  </si>
-  <si>
-    <t>Authorization_Required</t>
-  </si>
-  <si>
-    <t>Notes</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="60">
+  <si>
+    <t>Payer</t>
+  </si>
+  <si>
+    <t>Dataset_Type</t>
+  </si>
+  <si>
+    <t>CDF_Field</t>
+  </si>
+  <si>
+    <t>Business_Logic</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Synonyms</t>
   </si>
   <si>
     <t>UnitedHealthcare</t>
   </si>
   <si>
-    <t>Private</t>
-  </si>
-  <si>
-    <t>Nationwide (USA)</t>
-  </si>
-  <si>
-    <t>HMO, PPO, Medicare Advantage, Medicaid Managed Care</t>
-  </si>
-  <si>
-    <t>EDI 270/271; UHCprovider portal</t>
-  </si>
-  <si>
-    <t>EDI 837P/837I/837D via clearinghouse</t>
-  </si>
-  <si>
-    <t>Provider → Clearinghouse → UHC</t>
-  </si>
-  <si>
-    <t>HIPAA validation + adjudication system</t>
-  </si>
-  <si>
-    <t>7–21 days</t>
-  </si>
-  <si>
-    <t>EDI 835</t>
-  </si>
-  <si>
-    <t>Missing data, HIPAA edit failure, coding issues</t>
-  </si>
-  <si>
-    <t>Yes (EDI 278)</t>
-  </si>
-  <si>
-    <t>ANSI X12 format required; rejected claims not processed</t>
-  </si>
-  <si>
     <t>Anthem</t>
   </si>
   <si>
-    <t>HMO, PPO, EPO, POS</t>
-  </si>
-  <si>
-    <t>EDI 270/271; Availity portal</t>
-  </si>
-  <si>
-    <t>EDI 837 via Availity Gateway</t>
-  </si>
-  <si>
-    <t>Provider → Availity → Anthem</t>
-  </si>
-  <si>
-    <t>EDI validation + real-time processing</t>
-  </si>
-  <si>
-    <t>7–14 days</t>
-  </si>
-  <si>
-    <t>Missing provider ID, eligibility mismatch</t>
-  </si>
-  <si>
-    <t>Yes (via Availity)</t>
-  </si>
-  <si>
-    <t>Availity is mandatory gateway</t>
-  </si>
-  <si>
     <t>Cigna</t>
   </si>
   <si>
-    <t>Nationwide + Global</t>
-  </si>
-  <si>
-    <t>HMO, PPO, EPO, Dental, Behavioral</t>
-  </si>
-  <si>
-    <t>EDI 270/271; Provider portal</t>
-  </si>
-  <si>
-    <t>EDI via clearinghouse (837, 835, 278 etc.)</t>
-  </si>
-  <si>
-    <t>Provider → Clearinghouse → Cigna</t>
-  </si>
-  <si>
-    <t>Automated EDI processing reduces errors</t>
-  </si>
-  <si>
-    <t>7–15 days</t>
-  </si>
-  <si>
-    <t>Missing info, coding errors, no auth</t>
-  </si>
-  <si>
-    <t>Full EDI lifecycle supported</t>
+    <t>Aetna</t>
   </si>
   <si>
     <t>Highmark</t>
   </si>
   <si>
-    <t>Private (BCBS)</t>
-  </si>
-  <si>
-    <t>Regional (PA, WV, NY)</t>
-  </si>
-  <si>
-    <t>PPO, HMO, Medicare Advantage</t>
-  </si>
-  <si>
-    <t>EDI 270/271</t>
-  </si>
-  <si>
-    <t>EDI 837P/837I/837D; paper optional</t>
-  </si>
-  <si>
-    <t>Provider → Clearinghouse → Highmark</t>
-  </si>
-  <si>
-    <t>Electronic claims prioritized</t>
-  </si>
-  <si>
-    <t>10–20 days</t>
-  </si>
-  <si>
-    <t>Incomplete forms, invalid format</t>
-  </si>
-  <si>
-    <t>Trading partner enrollment required</t>
+    <t>ELIG</t>
+  </si>
+  <si>
+    <t>CLAIMS</t>
+  </si>
+  <si>
+    <t>RXCLAIMS</t>
+  </si>
+  <si>
+    <t>member_id</t>
+  </si>
+  <si>
+    <t>plan_id</t>
+  </si>
+  <si>
+    <t>effdate</t>
+  </si>
+  <si>
+    <t>termdate</t>
+  </si>
+  <si>
+    <t>group_id</t>
+  </si>
+  <si>
+    <t>claim_id</t>
+  </si>
+  <si>
+    <t>allowed_amount</t>
+  </si>
+  <si>
+    <t>rx_claim_id</t>
+  </si>
+  <si>
+    <t>drug_code</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(member_id))</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(plan_id))</t>
+  </si>
+  <si>
+    <t>CAST(coverage_start_date AS DATE)</t>
+  </si>
+  <si>
+    <t>CAST(coverage_end_date AS DATE)</t>
+  </si>
+  <si>
+    <t>REPLACE(group_number,'-','')</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(claim_id))</t>
+  </si>
+  <si>
+    <t>CAST(service_start_date AS DATE)</t>
+  </si>
+  <si>
+    <t>CAST(service_end_date AS DATE)</t>
+  </si>
+  <si>
+    <t>CAST(allowed_amount AS DECIMAL(10,2))</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(rx_claim_id))</t>
+  </si>
+  <si>
+    <t>CAST(fill_date AS DATE)</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(ndc_code))</t>
+  </si>
+  <si>
+    <t>Member Information</t>
+  </si>
+  <si>
+    <t>Plan Information</t>
+  </si>
+  <si>
+    <t>Coverage Dates</t>
+  </si>
+  <si>
+    <t>Group Information</t>
+  </si>
+  <si>
+    <t>Claim Information</t>
+  </si>
+  <si>
+    <t>General Mapping</t>
+  </si>
+  <si>
+    <t>member_id mapping: Converts text to uppercase, removes leading/trailing spaces.</t>
+  </si>
+  <si>
+    <t>plan_id mapping: Converts text to uppercase, removes leading/trailing spaces.</t>
+  </si>
+  <si>
+    <t>effdate mapping: casts value to target datatype/date.</t>
+  </si>
+  <si>
+    <t>termdate mapping: casts value to target datatype/date.</t>
+  </si>
+  <si>
+    <t>group_id mapping: replaces characters in source value.</t>
+  </si>
+  <si>
+    <t>claim_id mapping: Converts text to uppercase, removes leading/trailing spaces.</t>
+  </si>
+  <si>
+    <t>allowed_amount mapping: casts value to target datatype/date.</t>
+  </si>
+  <si>
+    <t>rx_claim_id mapping: Converts text to uppercase, removes leading/trailing spaces.</t>
+  </si>
+  <si>
+    <t>drug_code mapping: Converts text to uppercase, removes leading/trailing spaces.</t>
+  </si>
+  <si>
+    <t>member id, subscriber id, patient id</t>
+  </si>
+  <si>
+    <t>plan id, insurance plan, benefit plan</t>
+  </si>
+  <si>
+    <t>effective date, coverage start date, start date</t>
+  </si>
+  <si>
+    <t>termination date, coverage end date, end date</t>
+  </si>
+  <si>
+    <t>group id, employer group, group number</t>
+  </si>
+  <si>
+    <t>claim id, claim number</t>
+  </si>
+  <si>
+    <t>allowed amount</t>
+  </si>
+  <si>
+    <t>rx claim id</t>
+  </si>
+  <si>
+    <t>drug code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -214,7 +231,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -222,12 +239,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -288,7 +323,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -320,9 +355,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -354,6 +407,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -530,230 +601,1767 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="48.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="J2" t="s">
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="L2" t="s">
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E35" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="E39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E40" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
         <v>32</v>
       </c>
-      <c r="J3" t="s">
+      <c r="E41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
         <v>22</v>
       </c>
-      <c r="K3" t="s">
+      <c r="D42" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="s">
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" t="s">
         <v>34</v>
       </c>
-      <c r="M3" t="s">
+      <c r="E44" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="E46" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F47" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F48" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="s">
         <v>39</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F51" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" t="s">
         <v>40</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F52" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" t="s">
+        <v>44</v>
+      </c>
+      <c r="G54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" t="s">
+        <v>45</v>
+      </c>
+      <c r="G55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" t="s">
         <v>41</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F56" t="s">
+        <v>48</v>
+      </c>
+      <c r="G56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" t="s">
+        <v>49</v>
+      </c>
+      <c r="G57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" t="s">
         <v>42</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="s">
+        <v>34</v>
+      </c>
+      <c r="E60" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" t="s">
+        <v>45</v>
+      </c>
+      <c r="G60" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" t="s">
+        <v>50</v>
+      </c>
+      <c r="G61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" t="s">
+        <v>37</v>
+      </c>
+      <c r="F63" t="s">
         <v>43</v>
       </c>
-      <c r="J4" t="s">
+      <c r="G63" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" t="s">
+        <v>45</v>
+      </c>
+      <c r="G65" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" t="s">
+        <v>39</v>
+      </c>
+      <c r="F66" t="s">
+        <v>46</v>
+      </c>
+      <c r="G66" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" t="s">
+        <v>47</v>
+      </c>
+      <c r="G67" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" t="s">
+        <v>38</v>
+      </c>
+      <c r="F69" t="s">
+        <v>44</v>
+      </c>
+      <c r="G69" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" t="s">
+        <v>38</v>
+      </c>
+      <c r="F70" t="s">
+        <v>45</v>
+      </c>
+      <c r="G70" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" t="s">
+        <v>32</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71" t="s">
+        <v>48</v>
+      </c>
+      <c r="G71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" t="s">
         <v>22</v>
       </c>
-      <c r="K4" t="s">
+      <c r="D72" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" t="s">
+        <v>40</v>
+      </c>
+      <c r="F72" t="s">
+        <v>49</v>
+      </c>
+      <c r="G72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" t="s">
+        <v>36</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" t="s">
         <v>44</v>
       </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="G74" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G75" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" t="s">
         <v>50</v>
       </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" t="s">
-        <v>56</v>
+      <c r="G76" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/payers.xlsx
+++ b/data/payers.xlsx
@@ -1,27 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Alish\AI_CHAT_BOT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6287BEA4-6F3D-4F75-97E5-914BBEC4E17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79573AE-A392-4A52-9EFC-59C4F041D266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Mapping" sheetId="1" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" r:id="rId2"/>
+    <sheet name="CDF_Fields" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data_Mapping!$A$1:$F$169</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="549">
   <si>
     <t>DATASET_TYPE</t>
   </si>
@@ -254,12 +258,6 @@
     <t>Alphanumeric</t>
   </si>
   <si>
-    <t>Unique member id derived from enrid+dob+gender</t>
-  </si>
-  <si>
-    <t>Enrollment id</t>
-  </si>
-  <si>
     <t>CHAR</t>
   </si>
   <si>
@@ -486,14 +484,1210 @@
   </si>
   <si>
     <t>drg_emp_desc</t>
+  </si>
+  <si>
+    <t>memfirstname</t>
+  </si>
+  <si>
+    <t>memlastname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Null for Fully insured employer groups </t>
+  </si>
+  <si>
+    <t xml:space="preserve">billed amount </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 for UHC Rx claims </t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Billed amount &gt;= Allowed amount &gt;= paid amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOI (Mail Order Indicator) </t>
+  </si>
+  <si>
+    <t>Generally higher counts in 'R' Retails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days supply </t>
+  </si>
+  <si>
+    <t>Counts are generally higher in lower period and gradually decreasing</t>
+  </si>
+  <si>
+    <t>SSN/ Employee_num</t>
+  </si>
+  <si>
+    <t>Combination of SSN/ Employee_num, gender, dob conctenated with group id.  We must preserve the memberid during payer switch, so we need to make entry on rulestable namely hr_payer_swith_order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open termdates must be handled and are generally handled using sourcefilename and for some payer rulestable must be maintained </t>
+  </si>
+  <si>
+    <t>LOA's</t>
+  </si>
+  <si>
+    <t>LOAs are level of aggregation, and are differently configured for different clients from 1 to 5 or 6.</t>
+  </si>
+  <si>
+    <t>LOA1: Office region</t>
+  </si>
+  <si>
+    <t>LOA2: Payer name</t>
+  </si>
+  <si>
+    <t>LOA3: Group name</t>
+  </si>
+  <si>
+    <t>LOA4: Coverage status</t>
+  </si>
+  <si>
+    <t>LOA5: Planname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOA6: Location/ Family/ </t>
+  </si>
+  <si>
+    <t>cov_typ</t>
+  </si>
+  <si>
+    <t>Only medical, filter out Rx, dental and vision coverages</t>
+  </si>
+  <si>
+    <t>SIC Code</t>
+  </si>
+  <si>
+    <t>Standard Industrilised code and must be one for a group despite of payer switch, generally from onboarding form</t>
+  </si>
+  <si>
+    <t>Date must be from the time of group implemetation, runouts are valid and any gaps must be communicated with PM's</t>
+  </si>
+  <si>
+    <t>Data can be from prior to the time of it's implementation, runout not allowed and must be hard termed</t>
+  </si>
+  <si>
+    <t>row_id</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>addr1</t>
+  </si>
+  <si>
+    <t>addr2</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>zip</t>
+  </si>
+  <si>
+    <t>homephone</t>
+  </si>
+  <si>
+    <t>workphone</t>
+  </si>
+  <si>
+    <t>covtypeid</t>
+  </si>
+  <si>
+    <t>covtypedesc</t>
+  </si>
+  <si>
+    <t>orgeffdate</t>
+  </si>
+  <si>
+    <t>lti</t>
+  </si>
+  <si>
+    <t>lvlid1</t>
+  </si>
+  <si>
+    <t>lvldesc1</t>
+  </si>
+  <si>
+    <t>lvlid2</t>
+  </si>
+  <si>
+    <t>lvldesc2</t>
+  </si>
+  <si>
+    <t>lvlid3</t>
+  </si>
+  <si>
+    <t>lvldesc3</t>
+  </si>
+  <si>
+    <t>lvlid4</t>
+  </si>
+  <si>
+    <t>lvldesc4</t>
+  </si>
+  <si>
+    <t>lvlid5</t>
+  </si>
+  <si>
+    <t>lvldesc5</t>
+  </si>
+  <si>
+    <t>lvlid6</t>
+  </si>
+  <si>
+    <t>lvldesc6</t>
+  </si>
+  <si>
+    <t>lvlid7</t>
+  </si>
+  <si>
+    <t>lvldesc7</t>
+  </si>
+  <si>
+    <t>lvlid8</t>
+  </si>
+  <si>
+    <t>lvldesc8</t>
+  </si>
+  <si>
+    <t>lvlid9</t>
+  </si>
+  <si>
+    <t>lvldesc9</t>
+  </si>
+  <si>
+    <t>lvlid10</t>
+  </si>
+  <si>
+    <t>lvldesc10</t>
+  </si>
+  <si>
+    <t>cmstatus</t>
+  </si>
+  <si>
+    <t>pcpid</t>
+  </si>
+  <si>
+    <t>pcpname</t>
+  </si>
+  <si>
+    <t>ssn</t>
+  </si>
+  <si>
+    <t>bencovtype</t>
+  </si>
+  <si>
+    <t>bencovtypedesc</t>
+  </si>
+  <si>
+    <t>siccode</t>
+  </si>
+  <si>
+    <t>sicdesc</t>
+  </si>
+  <si>
+    <t>payertype</t>
+  </si>
+  <si>
+    <t>rcvmth</t>
+  </si>
+  <si>
+    <t>srcfilename</t>
+  </si>
+  <si>
+    <t>mem_uid</t>
+  </si>
+  <si>
+    <t>udf1</t>
+  </si>
+  <si>
+    <t>udf1_mem</t>
+  </si>
+  <si>
+    <t>udf2</t>
+  </si>
+  <si>
+    <t>udf2_mem</t>
+  </si>
+  <si>
+    <t>udfc1</t>
+  </si>
+  <si>
+    <t>udfc2</t>
+  </si>
+  <si>
+    <t>udfc3</t>
+  </si>
+  <si>
+    <t>udfc4</t>
+  </si>
+  <si>
+    <t>udfc5</t>
+  </si>
+  <si>
+    <t>udfc6</t>
+  </si>
+  <si>
+    <t>udfc7</t>
+  </si>
+  <si>
+    <t>udfc8</t>
+  </si>
+  <si>
+    <t>udfc9</t>
+  </si>
+  <si>
+    <t>udfc10</t>
+  </si>
+  <si>
+    <t>udfc11</t>
+  </si>
+  <si>
+    <t>udfc12</t>
+  </si>
+  <si>
+    <t>udfc13</t>
+  </si>
+  <si>
+    <t>udfc14</t>
+  </si>
+  <si>
+    <t>udfc15</t>
+  </si>
+  <si>
+    <t>udfc16</t>
+  </si>
+  <si>
+    <t>udfc17</t>
+  </si>
+  <si>
+    <t>udfc18</t>
+  </si>
+  <si>
+    <t>udfc19</t>
+  </si>
+  <si>
+    <t>udfc20</t>
+  </si>
+  <si>
+    <t>udfc21</t>
+  </si>
+  <si>
+    <t>udfc22</t>
+  </si>
+  <si>
+    <t>udfc23</t>
+  </si>
+  <si>
+    <t>udfc24</t>
+  </si>
+  <si>
+    <t>udfc25</t>
+  </si>
+  <si>
+    <t>udfc26</t>
+  </si>
+  <si>
+    <t>udfc27</t>
+  </si>
+  <si>
+    <t>udfc28</t>
+  </si>
+  <si>
+    <t>udfc29</t>
+  </si>
+  <si>
+    <t>udfc30</t>
+  </si>
+  <si>
+    <t>udfd1</t>
+  </si>
+  <si>
+    <t>udfd2</t>
+  </si>
+  <si>
+    <t>udfd3</t>
+  </si>
+  <si>
+    <t>udfd4</t>
+  </si>
+  <si>
+    <t>udfn1</t>
+  </si>
+  <si>
+    <t>udfn2</t>
+  </si>
+  <si>
+    <t>vh_lvl_id</t>
+  </si>
+  <si>
+    <t>elig_begin_date</t>
+  </si>
+  <si>
+    <t>elig_last_date</t>
+  </si>
+  <si>
+    <t>begin_dte</t>
+  </si>
+  <si>
+    <t>end_dte</t>
+  </si>
+  <si>
+    <t>fom_dte</t>
+  </si>
+  <si>
+    <t>elig_flag</t>
+  </si>
+  <si>
+    <t>hpemployee</t>
+  </si>
+  <si>
+    <t>emp_nbr</t>
+  </si>
+  <si>
+    <t>medeligcatid</t>
+  </si>
+  <si>
+    <t>productid</t>
+  </si>
+  <si>
+    <t>srcrelflag</t>
+  </si>
+  <si>
+    <t>coveragestatus</t>
+  </si>
+  <si>
+    <t>plantype</t>
+  </si>
+  <si>
+    <t>vhpayorid</t>
+  </si>
+  <si>
+    <t>vhlayoutid</t>
+  </si>
+  <si>
+    <t>empstatuscode</t>
+  </si>
+  <si>
+    <t>empstatusdesc</t>
+  </si>
+  <si>
+    <t>mcaid1</t>
+  </si>
+  <si>
+    <t>eligcat</t>
+  </si>
+  <si>
+    <t>orec</t>
+  </si>
+  <si>
+    <t>hospicecov</t>
+  </si>
+  <si>
+    <t>product_id_2</t>
+  </si>
+  <si>
+    <t>aifileid</t>
+  </si>
+  <si>
+    <t>airownumber</t>
+  </si>
+  <si>
+    <t>vhpayername</t>
+  </si>
+  <si>
+    <t>vhgroupname</t>
+  </si>
+  <si>
+    <t>plannumber</t>
+  </si>
+  <si>
+    <t>populationtype</t>
+  </si>
+  <si>
+    <t>race_id</t>
+  </si>
+  <si>
+    <t>dod</t>
+  </si>
+  <si>
+    <t>i_src_orcl_row_id</t>
+  </si>
+  <si>
+    <t>i_src_tbl_nm</t>
+  </si>
+  <si>
+    <t>empzip</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>lvl4firstname</t>
+  </si>
+  <si>
+    <t>lvl4lastname</t>
+  </si>
+  <si>
+    <t>subscriberflag</t>
+  </si>
+  <si>
+    <t>pbp_nbr</t>
+  </si>
+  <si>
+    <t>snp_type</t>
+  </si>
+  <si>
+    <t>amp_nbr</t>
+  </si>
+  <si>
+    <t>cin_number</t>
+  </si>
+  <si>
+    <t>fileid_rownum</t>
+  </si>
+  <si>
+    <t>table_name</t>
+  </si>
+  <si>
+    <t>layoutid</t>
+  </si>
+  <si>
+    <t>sn</t>
+  </si>
+  <si>
+    <t>transnum</t>
+  </si>
+  <si>
+    <t>seqno</t>
+  </si>
+  <si>
+    <t>datetimestamp</t>
+  </si>
+  <si>
+    <t>metricquantity</t>
+  </si>
+  <si>
+    <t>dayssupply</t>
+  </si>
+  <si>
+    <t>drugstrength</t>
+  </si>
+  <si>
+    <t>formulary_yn</t>
+  </si>
+  <si>
+    <t>moi</t>
+  </si>
+  <si>
+    <t>prescriberid</t>
+  </si>
+  <si>
+    <t>prescribertype</t>
+  </si>
+  <si>
+    <t>prescribername</t>
+  </si>
+  <si>
+    <t>prescribernpi</t>
+  </si>
+  <si>
+    <t>pharmid</t>
+  </si>
+  <si>
+    <t>pharmname</t>
+  </si>
+  <si>
+    <t>pharmnpi</t>
+  </si>
+  <si>
+    <t>pharmzipcode</t>
+  </si>
+  <si>
+    <t>ingredcost</t>
+  </si>
+  <si>
+    <t>dispensingcost</t>
+  </si>
+  <si>
+    <t>salestax</t>
+  </si>
+  <si>
+    <t>enrpaidamt</t>
+  </si>
+  <si>
+    <t>deductamt</t>
+  </si>
+  <si>
+    <t>notallowedamt</t>
+  </si>
+  <si>
+    <t>admfees</t>
+  </si>
+  <si>
+    <t>awp</t>
+  </si>
+  <si>
+    <t>cobamt</t>
+  </si>
+  <si>
+    <t>adjcode</t>
+  </si>
+  <si>
+    <t>claimstatus</t>
+  </si>
+  <si>
+    <t>supplyflag</t>
+  </si>
+  <si>
+    <t>discountamt</t>
+  </si>
+  <si>
+    <t>prescount</t>
+  </si>
+  <si>
+    <t>udfm1</t>
+  </si>
+  <si>
+    <t>udfm2</t>
+  </si>
+  <si>
+    <t>udf3</t>
+  </si>
+  <si>
+    <t>udf4</t>
+  </si>
+  <si>
+    <t>udf5</t>
+  </si>
+  <si>
+    <t>udf6</t>
+  </si>
+  <si>
+    <t>udf7</t>
+  </si>
+  <si>
+    <t>udf8</t>
+  </si>
+  <si>
+    <t>udf9</t>
+  </si>
+  <si>
+    <t>udfd5</t>
+  </si>
+  <si>
+    <t>udfn3</t>
+  </si>
+  <si>
+    <t>udfn4</t>
+  </si>
+  <si>
+    <t>udfn5</t>
+  </si>
+  <si>
+    <t>udfn6</t>
+  </si>
+  <si>
+    <t>udfn7</t>
+  </si>
+  <si>
+    <t>udfn8</t>
+  </si>
+  <si>
+    <t>udfn9</t>
+  </si>
+  <si>
+    <t>udfn10</t>
+  </si>
+  <si>
+    <t>udfn11</t>
+  </si>
+  <si>
+    <t>udfn12</t>
+  </si>
+  <si>
+    <t>udfn13</t>
+  </si>
+  <si>
+    <t>udfn14</t>
+  </si>
+  <si>
+    <t>udfn15</t>
+  </si>
+  <si>
+    <t>udfn16</t>
+  </si>
+  <si>
+    <t>udfn17</t>
+  </si>
+  <si>
+    <t>udfn18</t>
+  </si>
+  <si>
+    <t>udfn19</t>
+  </si>
+  <si>
+    <t>udfn20</t>
+  </si>
+  <si>
+    <t>qty_disp</t>
+  </si>
+  <si>
+    <t>compoundind</t>
+  </si>
+  <si>
+    <t>specialtyind</t>
+  </si>
+  <si>
+    <t>pharmnabpnum</t>
+  </si>
+  <si>
+    <t>dawps_cd</t>
+  </si>
+  <si>
+    <t>rx_orgn_cd</t>
+  </si>
+  <si>
+    <t>unc_price</t>
+  </si>
+  <si>
+    <t>drugtypecode</t>
+  </si>
+  <si>
+    <t>drugtypedesc</t>
+  </si>
+  <si>
+    <t>gcn</t>
+  </si>
+  <si>
+    <t>gi</t>
+  </si>
+  <si>
+    <t>gpi</t>
+  </si>
+  <si>
+    <t>rxcode</t>
+  </si>
+  <si>
+    <t>rxdesc</t>
+  </si>
+  <si>
+    <t>reinsamt</t>
+  </si>
+  <si>
+    <t>repricedamt</t>
+  </si>
+  <si>
+    <t>persistencefactor</t>
+  </si>
+  <si>
+    <t>networktype</t>
+  </si>
+  <si>
+    <t>enrollment_source</t>
+  </si>
+  <si>
+    <t>clmnum</t>
+  </si>
+  <si>
+    <t>claimlinenumber</t>
+  </si>
+  <si>
+    <t>sccf</t>
+  </si>
+  <si>
+    <t>clmtype</t>
+  </si>
+  <si>
+    <t>clmtypedesc</t>
+  </si>
+  <si>
+    <t>clmcategory</t>
+  </si>
+  <si>
+    <t>fromdate</t>
+  </si>
+  <si>
+    <t>todate</t>
+  </si>
+  <si>
+    <t>rcvdate</t>
+  </si>
+  <si>
+    <t>billtype</t>
+  </si>
+  <si>
+    <t>admission_status</t>
+  </si>
+  <si>
+    <t>poscode</t>
+  </si>
+  <si>
+    <t>posdesc</t>
+  </si>
+  <si>
+    <t>diagcode</t>
+  </si>
+  <si>
+    <t>diagdesc</t>
+  </si>
+  <si>
+    <t>firstdiagcode</t>
+  </si>
+  <si>
+    <t>firstdiagdesc</t>
+  </si>
+  <si>
+    <t>seconddiagcode</t>
+  </si>
+  <si>
+    <t>seconddiagdesc</t>
+  </si>
+  <si>
+    <t>thirddiagcode</t>
+  </si>
+  <si>
+    <t>thirddiagdesc</t>
+  </si>
+  <si>
+    <t>fourthdiagcode</t>
+  </si>
+  <si>
+    <t>fourthdiagdesc</t>
+  </si>
+  <si>
+    <t>fifthdiagcode</t>
+  </si>
+  <si>
+    <t>fifthdiagdesc</t>
+  </si>
+  <si>
+    <t>sixthdiagcode</t>
+  </si>
+  <si>
+    <t>sixthdiagdesc</t>
+  </si>
+  <si>
+    <t>seventhdiagcode</t>
+  </si>
+  <si>
+    <t>seventhdiagdesc</t>
+  </si>
+  <si>
+    <t>eighthdiagcode</t>
+  </si>
+  <si>
+    <t>eighthdiagdesc</t>
+  </si>
+  <si>
+    <t>ninthdiagcode</t>
+  </si>
+  <si>
+    <t>ninthdiagdesc</t>
+  </si>
+  <si>
+    <t>tenthdiagcode</t>
+  </si>
+  <si>
+    <t>tenthdiagdesc</t>
+  </si>
+  <si>
+    <t>proctype</t>
+  </si>
+  <si>
+    <t>proccode</t>
+  </si>
+  <si>
+    <t>procdesc</t>
+  </si>
+  <si>
+    <t>revcode</t>
+  </si>
+  <si>
+    <t>drgcode</t>
+  </si>
+  <si>
+    <t>modifiercode</t>
+  </si>
+  <si>
+    <t>modifierdesc</t>
+  </si>
+  <si>
+    <t>cpt4_1</t>
+  </si>
+  <si>
+    <t>cpt4_2</t>
+  </si>
+  <si>
+    <t>cpt4_3</t>
+  </si>
+  <si>
+    <t>hcpcs</t>
+  </si>
+  <si>
+    <t>hcpcs2</t>
+  </si>
+  <si>
+    <t>cptii</t>
+  </si>
+  <si>
+    <t>cptii2</t>
+  </si>
+  <si>
+    <t>modifiercode2</t>
+  </si>
+  <si>
+    <t>modifiercode3</t>
+  </si>
+  <si>
+    <t>modifiercode4</t>
+  </si>
+  <si>
+    <t>rxhcc</t>
+  </si>
+  <si>
+    <t>cvx</t>
+  </si>
+  <si>
+    <t>cptiimodifiercode</t>
+  </si>
+  <si>
+    <t>cptiimodifiercode2</t>
+  </si>
+  <si>
+    <t>pnindicator</t>
+  </si>
+  <si>
+    <t>hospital_id</t>
+  </si>
+  <si>
+    <t>revcode1</t>
+  </si>
+  <si>
+    <t>revcode2</t>
+  </si>
+  <si>
+    <t>revcode4</t>
+  </si>
+  <si>
+    <t>revcode3</t>
+  </si>
+  <si>
+    <t>revcode5</t>
+  </si>
+  <si>
+    <t>icd9proccode1</t>
+  </si>
+  <si>
+    <t>icd9proccode2</t>
+  </si>
+  <si>
+    <t>icd9proccode3</t>
+  </si>
+  <si>
+    <t>icd9proccode4</t>
+  </si>
+  <si>
+    <t>icd9proccode5</t>
+  </si>
+  <si>
+    <t>icd9proccode6</t>
+  </si>
+  <si>
+    <t>drgtype</t>
+  </si>
+  <si>
+    <t>drgidentifier</t>
+  </si>
+  <si>
+    <t>ipdays</t>
+  </si>
+  <si>
+    <t>dischstatus</t>
+  </si>
+  <si>
+    <t>typeofbill</t>
+  </si>
+  <si>
+    <t>provid</t>
+  </si>
+  <si>
+    <t>provname</t>
+  </si>
+  <si>
+    <t>providerfirstname</t>
+  </si>
+  <si>
+    <t>providerlastname</t>
+  </si>
+  <si>
+    <t>provnpi</t>
+  </si>
+  <si>
+    <t>provzipcode</t>
+  </si>
+  <si>
+    <t>servtypecode</t>
+  </si>
+  <si>
+    <t>servtypedesc</t>
+  </si>
+  <si>
+    <t>provtypecode</t>
+  </si>
+  <si>
+    <t>provtypedesc</t>
+  </si>
+  <si>
+    <t>servicecode</t>
+  </si>
+  <si>
+    <t>specrollupcode</t>
+  </si>
+  <si>
+    <t>specrollupdesc</t>
+  </si>
+  <si>
+    <t>nwkid</t>
+  </si>
+  <si>
+    <t>nwkname</t>
+  </si>
+  <si>
+    <t>innwk</t>
+  </si>
+  <si>
+    <t>serviceunits</t>
+  </si>
+  <si>
+    <t>pposavingamt</t>
+  </si>
+  <si>
+    <t>planexclamt</t>
+  </si>
+  <si>
+    <t>labtestdata</t>
+  </si>
+  <si>
+    <t>sourceform</t>
+  </si>
+  <si>
+    <t>sourcetype</t>
+  </si>
+  <si>
+    <t>paiddays</t>
+  </si>
+  <si>
+    <t>icdtype</t>
+  </si>
+  <si>
+    <t>clmheadernumber</t>
+  </si>
+  <si>
+    <t>nchclmtypecode</t>
+  </si>
+  <si>
+    <t>admittype</t>
+  </si>
+  <si>
+    <t>admitsource</t>
+  </si>
+  <si>
+    <t>mdcr_npmt_rsn_cd</t>
+  </si>
+  <si>
+    <t>prov_ccn</t>
+  </si>
+  <si>
+    <t>clm_adjsmt_type_cd</t>
+  </si>
+  <si>
+    <t>clm_query_cd</t>
+  </si>
+  <si>
+    <t>prncpl_diag_cd</t>
+  </si>
+  <si>
+    <t>admtg_diag_cd</t>
+  </si>
+  <si>
+    <t>hdr_from_dt</t>
+  </si>
+  <si>
+    <t>hdr_thru_dt</t>
+  </si>
+  <si>
+    <t>op_srvc_typ_cd</t>
+  </si>
+  <si>
+    <t>refrngprovid</t>
+  </si>
+  <si>
+    <t>refrngprovname</t>
+  </si>
+  <si>
+    <t>refrngprovnpi</t>
+  </si>
+  <si>
+    <t>billngprovid</t>
+  </si>
+  <si>
+    <t>billngprovname</t>
+  </si>
+  <si>
+    <t>billngprovnpi</t>
+  </si>
+  <si>
+    <t>billngprovtaxid</t>
+  </si>
+  <si>
+    <t>srvcngprovid</t>
+  </si>
+  <si>
+    <t>srvcngprovname</t>
+  </si>
+  <si>
+    <t>srvcngprovnpi</t>
+  </si>
+  <si>
+    <t>atndngprovid</t>
+  </si>
+  <si>
+    <t>atndngprovname</t>
+  </si>
+  <si>
+    <t>atndngprovnpi</t>
+  </si>
+  <si>
+    <t>oprtngprovid</t>
+  </si>
+  <si>
+    <t>oprtngprovname</t>
+  </si>
+  <si>
+    <t>oprtngprovnpi</t>
+  </si>
+  <si>
+    <t>otherprov1id</t>
+  </si>
+  <si>
+    <t>otherprov1name</t>
+  </si>
+  <si>
+    <t>otherprov1npi</t>
+  </si>
+  <si>
+    <t>otherprov2id</t>
+  </si>
+  <si>
+    <t>otherprov2name</t>
+  </si>
+  <si>
+    <t>otherprov2npi</t>
+  </si>
+  <si>
+    <t>payment_type_cd</t>
+  </si>
+  <si>
+    <t>poa_firstdiagcode</t>
+  </si>
+  <si>
+    <t>poa_seconddiagcode</t>
+  </si>
+  <si>
+    <t>poa_thirddiagcode</t>
+  </si>
+  <si>
+    <t>poa_fourthdiagcode</t>
+  </si>
+  <si>
+    <t>poa_fifthdiagcode</t>
+  </si>
+  <si>
+    <t>poa_sixthdiagcode</t>
+  </si>
+  <si>
+    <t>poa_seventhdiagcode</t>
+  </si>
+  <si>
+    <t>poa_eighthdiagcode</t>
+  </si>
+  <si>
+    <t>poa_ninthdiagcode</t>
+  </si>
+  <si>
+    <t>poa_tenthdiagcode</t>
+  </si>
+  <si>
+    <t>poa_prncpl_diag_cd</t>
+  </si>
+  <si>
+    <t>poa_admtg_diag_cd</t>
+  </si>
+  <si>
+    <t>adjflag</t>
+  </si>
+  <si>
+    <t>dischrgind</t>
+  </si>
+  <si>
+    <t>dupcheck</t>
+  </si>
+  <si>
+    <t>fundcode</t>
+  </si>
+  <si>
+    <t>funddesc</t>
+  </si>
+  <si>
+    <t>grosscharge</t>
+  </si>
+  <si>
+    <t>iuou</t>
+  </si>
+  <si>
+    <t>nwkcity</t>
+  </si>
+  <si>
+    <t>nwkstate</t>
+  </si>
+  <si>
+    <t>ooa</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>provcity</t>
+  </si>
+  <si>
+    <t>provpres_yn</t>
+  </si>
+  <si>
+    <t>provstate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -521,8 +1715,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -826,17 +2021,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F169"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="122.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="122.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +2051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -876,7 +2071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -896,7 +2091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -916,7 +2111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -936,7 +2131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -956,7 +2151,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -976,7 +2171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -996,7 +2191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1016,7 +2211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1036,7 +2231,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1056,7 +2251,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1076,7 +2271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1096,7 +2291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1116,7 +2311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1136,7 +2331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1156,7 +2351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1176,7 +2371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1196,7 +2391,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1216,7 +2411,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1236,7 +2431,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1256,7 +2451,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1276,7 +2471,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1296,7 +2491,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1316,7 +2511,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1336,7 +2531,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1356,7 +2551,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1376,7 +2571,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -1396,7 +2591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -1416,7 +2611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -1436,7 +2631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -1456,7 +2651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -1476,7 +2671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -1496,7 +2691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -1516,7 +2711,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -1536,7 +2731,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>51</v>
       </c>
@@ -1556,7 +2751,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -1576,7 +2771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -1596,7 +2791,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -1616,7 +2811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -1636,7 +2831,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -1656,7 +2851,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -1676,7 +2871,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -1696,7 +2891,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1716,7 +2911,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1736,7 +2931,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1756,7 +2951,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1776,7 +2971,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1793,10 +2988,10 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1816,7 +3011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1833,10 +3028,10 @@
         <v>22</v>
       </c>
       <c r="F50" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1853,10 +3048,10 @@
         <v>24</v>
       </c>
       <c r="F51" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1873,10 +3068,10 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -1893,10 +3088,10 @@
         <v>28</v>
       </c>
       <c r="F53" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>30</v>
       </c>
@@ -1916,7 +3111,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>30</v>
       </c>
@@ -1936,7 +3131,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>30</v>
       </c>
@@ -1956,7 +3151,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>30</v>
       </c>
@@ -1976,7 +3171,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>30</v>
       </c>
@@ -1996,7 +3191,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>30</v>
       </c>
@@ -2013,10 +3208,10 @@
         <v>22</v>
       </c>
       <c r="F59" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>30</v>
       </c>
@@ -2033,10 +3228,10 @@
         <v>31</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
@@ -2053,10 +3248,10 @@
         <v>33</v>
       </c>
       <c r="F61" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>30</v>
       </c>
@@ -2076,7 +3271,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>30</v>
       </c>
@@ -2093,10 +3288,10 @@
         <v>37</v>
       </c>
       <c r="F63" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>30</v>
       </c>
@@ -2116,7 +3311,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -2133,10 +3328,10 @@
         <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>30</v>
       </c>
@@ -2153,10 +3348,10 @@
         <v>43</v>
       </c>
       <c r="F66" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -2173,10 +3368,10 @@
         <v>45</v>
       </c>
       <c r="F67" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>30</v>
       </c>
@@ -2193,10 +3388,10 @@
         <v>47</v>
       </c>
       <c r="F68" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -2213,10 +3408,10 @@
         <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -2236,7 +3431,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>51</v>
       </c>
@@ -2256,7 +3451,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>51</v>
       </c>
@@ -2276,7 +3471,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>51</v>
       </c>
@@ -2296,7 +3491,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>51</v>
       </c>
@@ -2316,7 +3511,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>51</v>
       </c>
@@ -2333,10 +3528,10 @@
         <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>51</v>
       </c>
@@ -2353,10 +3548,10 @@
         <v>52</v>
       </c>
       <c r="F76" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>51</v>
       </c>
@@ -2373,10 +3568,10 @@
         <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>51</v>
       </c>
@@ -2396,7 +3591,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>51</v>
       </c>
@@ -2413,10 +3608,10 @@
         <v>37</v>
       </c>
       <c r="F79" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>51</v>
       </c>
@@ -2436,7 +3631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>51</v>
       </c>
@@ -2453,10 +3648,10 @@
         <v>41</v>
       </c>
       <c r="F81" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>51</v>
       </c>
@@ -2473,10 +3668,10 @@
         <v>43</v>
       </c>
       <c r="F82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>51</v>
       </c>
@@ -2493,10 +3688,10 @@
         <v>45</v>
       </c>
       <c r="F83" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>51</v>
       </c>
@@ -2513,10 +3708,10 @@
         <v>54</v>
       </c>
       <c r="F84" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>51</v>
       </c>
@@ -2533,10 +3728,10 @@
         <v>56</v>
       </c>
       <c r="F85" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>7</v>
       </c>
@@ -2553,10 +3748,10 @@
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -2573,10 +3768,10 @@
         <v>12</v>
       </c>
       <c r="F87" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -2593,10 +3788,10 @@
         <v>14</v>
       </c>
       <c r="F88" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -2613,10 +3808,10 @@
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -2633,10 +3828,10 @@
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -2653,10 +3848,10 @@
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -2673,10 +3868,10 @@
         <v>22</v>
       </c>
       <c r="F92" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2693,10 +3888,10 @@
         <v>24</v>
       </c>
       <c r="F93" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -2713,10 +3908,10 @@
         <v>26</v>
       </c>
       <c r="F94" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -2733,10 +3928,10 @@
         <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -2753,10 +3948,10 @@
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -2773,10 +3968,10 @@
         <v>12</v>
       </c>
       <c r="F97" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -2793,10 +3988,10 @@
         <v>14</v>
       </c>
       <c r="F98" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -2813,10 +4008,10 @@
         <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>30</v>
       </c>
@@ -2833,10 +4028,10 @@
         <v>20</v>
       </c>
       <c r="F100" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -2853,10 +4048,10 @@
         <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>30</v>
       </c>
@@ -2873,10 +4068,10 @@
         <v>31</v>
       </c>
       <c r="F102" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -2893,10 +4088,10 @@
         <v>33</v>
       </c>
       <c r="F103" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>30</v>
       </c>
@@ -2913,10 +4108,10 @@
         <v>35</v>
       </c>
       <c r="F104" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>30</v>
       </c>
@@ -2933,10 +4128,10 @@
         <v>37</v>
       </c>
       <c r="F105" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>30</v>
       </c>
@@ -2953,10 +4148,10 @@
         <v>39</v>
       </c>
       <c r="F106" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>30</v>
       </c>
@@ -2973,10 +4168,10 @@
         <v>41</v>
       </c>
       <c r="F107" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>30</v>
       </c>
@@ -2993,10 +4188,10 @@
         <v>43</v>
       </c>
       <c r="F108" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>30</v>
       </c>
@@ -3016,7 +4211,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>30</v>
       </c>
@@ -3033,10 +4228,10 @@
         <v>47</v>
       </c>
       <c r="F110" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>30</v>
       </c>
@@ -3053,10 +4248,10 @@
         <v>49</v>
       </c>
       <c r="F111" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>51</v>
       </c>
@@ -3073,10 +4268,10 @@
         <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>51</v>
       </c>
@@ -3093,10 +4288,10 @@
         <v>12</v>
       </c>
       <c r="F113" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>51</v>
       </c>
@@ -3113,10 +4308,10 @@
         <v>14</v>
       </c>
       <c r="F114" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>51</v>
       </c>
@@ -3133,10 +4328,10 @@
         <v>16</v>
       </c>
       <c r="F115" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>51</v>
       </c>
@@ -3153,10 +4348,10 @@
         <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>51</v>
       </c>
@@ -3173,10 +4368,10 @@
         <v>22</v>
       </c>
       <c r="F117" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>51</v>
       </c>
@@ -3193,10 +4388,10 @@
         <v>52</v>
       </c>
       <c r="F118" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>51</v>
       </c>
@@ -3213,10 +4408,10 @@
         <v>33</v>
       </c>
       <c r="F119" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>51</v>
       </c>
@@ -3233,10 +4428,10 @@
         <v>35</v>
       </c>
       <c r="F120" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>51</v>
       </c>
@@ -3253,10 +4448,10 @@
         <v>37</v>
       </c>
       <c r="F121" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>51</v>
       </c>
@@ -3273,10 +4468,10 @@
         <v>39</v>
       </c>
       <c r="F122" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>51</v>
       </c>
@@ -3293,10 +4488,10 @@
         <v>41</v>
       </c>
       <c r="F123" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>51</v>
       </c>
@@ -3313,10 +4508,10 @@
         <v>43</v>
       </c>
       <c r="F124" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>51</v>
       </c>
@@ -3336,7 +4531,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>51</v>
       </c>
@@ -3353,10 +4548,10 @@
         <v>54</v>
       </c>
       <c r="F126" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>51</v>
       </c>
@@ -3373,10 +4568,10 @@
         <v>56</v>
       </c>
       <c r="F127" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -3393,10 +4588,10 @@
         <v>10</v>
       </c>
       <c r="F128" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -3413,10 +4608,10 @@
         <v>12</v>
       </c>
       <c r="F129" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -3433,10 +4628,10 @@
         <v>14</v>
       </c>
       <c r="F130" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>7</v>
       </c>
@@ -3453,10 +4648,10 @@
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>7</v>
       </c>
@@ -3473,10 +4668,10 @@
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>7</v>
       </c>
@@ -3493,10 +4688,10 @@
         <v>20</v>
       </c>
       <c r="F133" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3513,10 +4708,10 @@
         <v>22</v>
       </c>
       <c r="F134" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>7</v>
       </c>
@@ -3533,10 +4728,10 @@
         <v>24</v>
       </c>
       <c r="F135" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -3553,10 +4748,10 @@
         <v>26</v>
       </c>
       <c r="F136" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>7</v>
       </c>
@@ -3573,10 +4768,10 @@
         <v>28</v>
       </c>
       <c r="F137" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>30</v>
       </c>
@@ -3593,10 +4788,10 @@
         <v>10</v>
       </c>
       <c r="F138" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>30</v>
       </c>
@@ -3613,10 +4808,10 @@
         <v>12</v>
       </c>
       <c r="F139" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>30</v>
       </c>
@@ -3633,10 +4828,10 @@
         <v>14</v>
       </c>
       <c r="F140" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>30</v>
       </c>
@@ -3653,10 +4848,10 @@
         <v>16</v>
       </c>
       <c r="F141" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>30</v>
       </c>
@@ -3673,10 +4868,10 @@
         <v>20</v>
       </c>
       <c r="F142" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>30</v>
       </c>
@@ -3693,10 +4888,10 @@
         <v>22</v>
       </c>
       <c r="F143" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>30</v>
       </c>
@@ -3713,10 +4908,10 @@
         <v>31</v>
       </c>
       <c r="F144" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>30</v>
       </c>
@@ -3733,10 +4928,10 @@
         <v>33</v>
       </c>
       <c r="F145" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>30</v>
       </c>
@@ -3756,7 +4951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>30</v>
       </c>
@@ -3773,10 +4968,10 @@
         <v>37</v>
       </c>
       <c r="F147" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>30</v>
       </c>
@@ -3796,7 +4991,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>30</v>
       </c>
@@ -3813,10 +5008,10 @@
         <v>41</v>
       </c>
       <c r="F149" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>30</v>
       </c>
@@ -3833,10 +5028,10 @@
         <v>43</v>
       </c>
       <c r="F150" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>30</v>
       </c>
@@ -3853,10 +5048,10 @@
         <v>45</v>
       </c>
       <c r="F151" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>30</v>
       </c>
@@ -3873,10 +5068,10 @@
         <v>47</v>
       </c>
       <c r="F152" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>30</v>
       </c>
@@ -3893,10 +5088,10 @@
         <v>49</v>
       </c>
       <c r="F153" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>51</v>
       </c>
@@ -3913,10 +5108,10 @@
         <v>10</v>
       </c>
       <c r="F154" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>51</v>
       </c>
@@ -3933,10 +5128,10 @@
         <v>12</v>
       </c>
       <c r="F155" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>51</v>
       </c>
@@ -3953,10 +5148,10 @@
         <v>14</v>
       </c>
       <c r="F156" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>51</v>
       </c>
@@ -3973,10 +5168,10 @@
         <v>16</v>
       </c>
       <c r="F157" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>51</v>
       </c>
@@ -3993,10 +5188,10 @@
         <v>20</v>
       </c>
       <c r="F158" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>51</v>
       </c>
@@ -4013,10 +5208,10 @@
         <v>22</v>
       </c>
       <c r="F159" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -4033,10 +5228,10 @@
         <v>52</v>
       </c>
       <c r="F160" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>51</v>
       </c>
@@ -4053,10 +5248,10 @@
         <v>33</v>
       </c>
       <c r="F161" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>51</v>
       </c>
@@ -4076,7 +5271,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>51</v>
       </c>
@@ -4093,10 +5288,10 @@
         <v>37</v>
       </c>
       <c r="F163" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>51</v>
       </c>
@@ -4116,7 +5311,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>51</v>
       </c>
@@ -4133,10 +5328,10 @@
         <v>41</v>
       </c>
       <c r="F165" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>51</v>
       </c>
@@ -4153,10 +5348,10 @@
         <v>43</v>
       </c>
       <c r="F166" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>51</v>
       </c>
@@ -4173,10 +5368,10 @@
         <v>45</v>
       </c>
       <c r="F167" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>51</v>
       </c>
@@ -4193,10 +5388,10 @@
         <v>54</v>
       </c>
       <c r="F168" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>51</v>
       </c>
@@ -4213,7 +5408,7 @@
         <v>56</v>
       </c>
       <c r="F169" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4223,16 +5418,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -4246,7 +5441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -4257,10 +5452,10 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4271,66 +5466,2792 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
         <v>79</v>
       </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
         <v>82</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
         <v>83</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D8" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
         <v>86</v>
       </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C316"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>201</v>
+      </c>
+      <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>211</v>
+      </c>
+      <c r="B41" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" t="s">
+        <v>213</v>
+      </c>
+      <c r="C43" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" t="s">
+        <v>395</v>
+      </c>
+      <c r="C44" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
+        <v>396</v>
+      </c>
+      <c r="C45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" t="s">
+        <v>397</v>
+      </c>
+      <c r="C47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" t="s">
+        <v>398</v>
+      </c>
+      <c r="C49" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>220</v>
+      </c>
+      <c r="B50" t="s">
+        <v>399</v>
+      </c>
+      <c r="C50" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" t="s">
+        <v>400</v>
+      </c>
+      <c r="C51" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" t="s">
+        <v>401</v>
+      </c>
+      <c r="C52" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>225</v>
+      </c>
+      <c r="B55" t="s">
+        <v>402</v>
+      </c>
+      <c r="C55" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" t="s">
+        <v>403</v>
+      </c>
+      <c r="C56" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" t="s">
+        <v>404</v>
+      </c>
+      <c r="C57" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>228</v>
+      </c>
+      <c r="B58" t="s">
+        <v>405</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" t="s">
+        <v>406</v>
+      </c>
+      <c r="C59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" t="s">
+        <v>407</v>
+      </c>
+      <c r="C60" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>231</v>
+      </c>
+      <c r="B61" t="s">
+        <v>408</v>
+      </c>
+      <c r="C61" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>232</v>
+      </c>
+      <c r="B62" t="s">
+        <v>409</v>
+      </c>
+      <c r="C62" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>233</v>
+      </c>
+      <c r="B63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>234</v>
+      </c>
+      <c r="B64" t="s">
+        <v>411</v>
+      </c>
+      <c r="C64" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>235</v>
+      </c>
+      <c r="B65" t="s">
+        <v>412</v>
+      </c>
+      <c r="C65" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>236</v>
+      </c>
+      <c r="B66" t="s">
+        <v>413</v>
+      </c>
+      <c r="C66" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" t="s">
+        <v>414</v>
+      </c>
+      <c r="C67" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>238</v>
+      </c>
+      <c r="B68" t="s">
+        <v>415</v>
+      </c>
+      <c r="C68" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>239</v>
+      </c>
+      <c r="B69" t="s">
+        <v>416</v>
+      </c>
+      <c r="C69" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>240</v>
+      </c>
+      <c r="B70" t="s">
+        <v>417</v>
+      </c>
+      <c r="C70" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" t="s">
+        <v>418</v>
+      </c>
+      <c r="C71" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" t="s">
+        <v>419</v>
+      </c>
+      <c r="C72" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" t="s">
+        <v>420</v>
+      </c>
+      <c r="C73" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>244</v>
+      </c>
+      <c r="B74" t="s">
+        <v>421</v>
+      </c>
+      <c r="C74" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>245</v>
+      </c>
+      <c r="B75" t="s">
+        <v>422</v>
+      </c>
+      <c r="C75" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>246</v>
+      </c>
+      <c r="B76" t="s">
+        <v>423</v>
+      </c>
+      <c r="C76" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>247</v>
+      </c>
+      <c r="B77" t="s">
+        <v>424</v>
+      </c>
+      <c r="C77" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>248</v>
+      </c>
+      <c r="B78" t="s">
+        <v>425</v>
+      </c>
+      <c r="C78" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>249</v>
+      </c>
+      <c r="B79" t="s">
+        <v>426</v>
+      </c>
+      <c r="C79" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" t="s">
+        <v>427</v>
+      </c>
+      <c r="C80" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>251</v>
+      </c>
+      <c r="B81" t="s">
+        <v>428</v>
+      </c>
+      <c r="C81" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>252</v>
+      </c>
+      <c r="B82" t="s">
+        <v>429</v>
+      </c>
+      <c r="C82" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>253</v>
+      </c>
+      <c r="B83" t="s">
+        <v>430</v>
+      </c>
+      <c r="C83" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" t="s">
+        <v>431</v>
+      </c>
+      <c r="C84" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>255</v>
+      </c>
+      <c r="B85" t="s">
+        <v>432</v>
+      </c>
+      <c r="C85" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>256</v>
+      </c>
+      <c r="B86" t="s">
+        <v>433</v>
+      </c>
+      <c r="C86" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" t="s">
+        <v>434</v>
+      </c>
+      <c r="C87" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>258</v>
+      </c>
+      <c r="B88" t="s">
+        <v>435</v>
+      </c>
+      <c r="C88" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>259</v>
+      </c>
+      <c r="B89" t="s">
+        <v>436</v>
+      </c>
+      <c r="C89" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>260</v>
+      </c>
+      <c r="B90" t="s">
+        <v>437</v>
+      </c>
+      <c r="C90" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>261</v>
+      </c>
+      <c r="B91" t="s">
+        <v>438</v>
+      </c>
+      <c r="C91" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" t="s">
+        <v>439</v>
+      </c>
+      <c r="C92" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>263</v>
+      </c>
+      <c r="B93" t="s">
+        <v>440</v>
+      </c>
+      <c r="C93" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>264</v>
+      </c>
+      <c r="B94" t="s">
+        <v>441</v>
+      </c>
+      <c r="C94" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>265</v>
+      </c>
+      <c r="B95" t="s">
+        <v>442</v>
+      </c>
+      <c r="C95" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>266</v>
+      </c>
+      <c r="B96" t="s">
+        <v>443</v>
+      </c>
+      <c r="C96" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>267</v>
+      </c>
+      <c r="B97" t="s">
+        <v>444</v>
+      </c>
+      <c r="C97" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>268</v>
+      </c>
+      <c r="B98" t="s">
+        <v>445</v>
+      </c>
+      <c r="C98" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>269</v>
+      </c>
+      <c r="B99" t="s">
+        <v>446</v>
+      </c>
+      <c r="C99" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>270</v>
+      </c>
+      <c r="B100" t="s">
+        <v>447</v>
+      </c>
+      <c r="C100" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>271</v>
+      </c>
+      <c r="B101" t="s">
+        <v>448</v>
+      </c>
+      <c r="C101" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>272</v>
+      </c>
+      <c r="B102" t="s">
+        <v>449</v>
+      </c>
+      <c r="C102" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>273</v>
+      </c>
+      <c r="B103" t="s">
+        <v>450</v>
+      </c>
+      <c r="C103" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>274</v>
+      </c>
+      <c r="B104" t="s">
+        <v>451</v>
+      </c>
+      <c r="C104" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>275</v>
+      </c>
+      <c r="B105" t="s">
+        <v>452</v>
+      </c>
+      <c r="C105" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>276</v>
+      </c>
+      <c r="B106" t="s">
+        <v>453</v>
+      </c>
+      <c r="C106" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>277</v>
+      </c>
+      <c r="B107" t="s">
+        <v>454</v>
+      </c>
+      <c r="C107" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>278</v>
+      </c>
+      <c r="B108" t="s">
+        <v>455</v>
+      </c>
+      <c r="C108" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>279</v>
+      </c>
+      <c r="B109" t="s">
+        <v>456</v>
+      </c>
+      <c r="C109" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" t="s">
+        <v>457</v>
+      </c>
+      <c r="C110" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>280</v>
+      </c>
+      <c r="B111" t="s">
+        <v>458</v>
+      </c>
+      <c r="C111" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>281</v>
+      </c>
+      <c r="B112" t="s">
+        <v>459</v>
+      </c>
+      <c r="C112" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>282</v>
+      </c>
+      <c r="B113" t="s">
+        <v>460</v>
+      </c>
+      <c r="C113" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>283</v>
+      </c>
+      <c r="B114" t="s">
+        <v>461</v>
+      </c>
+      <c r="C114" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>284</v>
+      </c>
+      <c r="B115" t="s">
+        <v>462</v>
+      </c>
+      <c r="C115" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>285</v>
+      </c>
+      <c r="B116" t="s">
+        <v>338</v>
+      </c>
+      <c r="C116" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>286</v>
+      </c>
+      <c r="B117" t="s">
+        <v>337</v>
+      </c>
+      <c r="C117" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>287</v>
+      </c>
+      <c r="B118" t="s">
+        <v>463</v>
+      </c>
+      <c r="C118" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>288</v>
+      </c>
+      <c r="B119" t="s">
+        <v>464</v>
+      </c>
+      <c r="C119" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>289</v>
+      </c>
+      <c r="B120" t="s">
+        <v>465</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>290</v>
+      </c>
+      <c r="B121" t="s">
+        <v>466</v>
+      </c>
+      <c r="C121" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>291</v>
+      </c>
+      <c r="B122" t="s">
+        <v>467</v>
+      </c>
+      <c r="C122" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>292</v>
+      </c>
+      <c r="B123" t="s">
+        <v>468</v>
+      </c>
+      <c r="C123" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>293</v>
+      </c>
+      <c r="B124" t="s">
+        <v>469</v>
+      </c>
+      <c r="C124" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>294</v>
+      </c>
+      <c r="B125" t="s">
+        <v>470</v>
+      </c>
+      <c r="C125" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>295</v>
+      </c>
+      <c r="B126" t="s">
+        <v>471</v>
+      </c>
+      <c r="C126" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>296</v>
+      </c>
+      <c r="B127" t="s">
+        <v>472</v>
+      </c>
+      <c r="C127" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>297</v>
+      </c>
+      <c r="B128" t="s">
+        <v>473</v>
+      </c>
+      <c r="C128" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>298</v>
+      </c>
+      <c r="B129" t="s">
+        <v>474</v>
+      </c>
+      <c r="C129" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>299</v>
+      </c>
+      <c r="B130" t="s">
+        <v>475</v>
+      </c>
+      <c r="C130" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>300</v>
+      </c>
+      <c r="B131" t="s">
+        <v>476</v>
+      </c>
+      <c r="C131" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>301</v>
+      </c>
+      <c r="B132" t="s">
+        <v>477</v>
+      </c>
+      <c r="C132" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>302</v>
+      </c>
+      <c r="B133" t="s">
+        <v>478</v>
+      </c>
+      <c r="C133" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>303</v>
+      </c>
+      <c r="B134" t="s">
+        <v>387</v>
+      </c>
+      <c r="C134" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>304</v>
+      </c>
+      <c r="B135" t="s">
+        <v>479</v>
+      </c>
+      <c r="C135" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>305</v>
+      </c>
+      <c r="B136" t="s">
+        <v>35</v>
+      </c>
+      <c r="C136" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" t="s">
+        <v>39</v>
+      </c>
+      <c r="C138" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>308</v>
+      </c>
+      <c r="B139" t="s">
+        <v>480</v>
+      </c>
+      <c r="C139" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" t="s">
+        <v>331</v>
+      </c>
+      <c r="C140" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>310</v>
+      </c>
+      <c r="B141" t="s">
+        <v>43</v>
+      </c>
+      <c r="C141" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B142" t="s">
+        <v>45</v>
+      </c>
+      <c r="C142" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B143" t="s">
+        <v>332</v>
+      </c>
+      <c r="C143" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B144" t="s">
+        <v>333</v>
+      </c>
+      <c r="C144" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B145" t="s">
+        <v>336</v>
+      </c>
+      <c r="C145" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B146" t="s">
+        <v>481</v>
+      </c>
+      <c r="C146" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B147" t="s">
+        <v>482</v>
+      </c>
+      <c r="C147" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B148" t="s">
+        <v>220</v>
+      </c>
+      <c r="C148" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B149" t="s">
+        <v>221</v>
+      </c>
+      <c r="C149" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B150" t="s">
+        <v>217</v>
+      </c>
+      <c r="C150" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B151" t="s">
+        <v>223</v>
+      </c>
+      <c r="C151" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B152" t="s">
+        <v>224</v>
+      </c>
+      <c r="C152" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B153" t="s">
+        <v>483</v>
+      </c>
+      <c r="C153" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B154" t="s">
+        <v>484</v>
+      </c>
+      <c r="C154" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B155" t="s">
+        <v>225</v>
+      </c>
+      <c r="C155" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B156" t="s">
+        <v>342</v>
+      </c>
+      <c r="C156" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B157" t="s">
+        <v>343</v>
+      </c>
+      <c r="C157" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B158" t="s">
+        <v>226</v>
+      </c>
+      <c r="C158" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B159" t="s">
+        <v>228</v>
+      </c>
+      <c r="C159" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B160" t="s">
+        <v>344</v>
+      </c>
+      <c r="C160" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B161" t="s">
+        <v>345</v>
+      </c>
+      <c r="C161" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B162" t="s">
+        <v>346</v>
+      </c>
+      <c r="C162" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B163" t="s">
+        <v>347</v>
+      </c>
+      <c r="C163" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B164" t="s">
+        <v>348</v>
+      </c>
+      <c r="C164" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B165" t="s">
+        <v>349</v>
+      </c>
+      <c r="C165" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B166" t="s">
+        <v>350</v>
+      </c>
+      <c r="C166" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B167" t="s">
+        <v>230</v>
+      </c>
+      <c r="C167" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B168" t="s">
+        <v>231</v>
+      </c>
+      <c r="C168" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B169" t="s">
+        <v>232</v>
+      </c>
+      <c r="C169" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B170" t="s">
+        <v>233</v>
+      </c>
+      <c r="C170" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B171" t="s">
+        <v>234</v>
+      </c>
+      <c r="C171" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B172" t="s">
+        <v>235</v>
+      </c>
+      <c r="C172" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B173" t="s">
+        <v>236</v>
+      </c>
+      <c r="C173" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B174" t="s">
+        <v>237</v>
+      </c>
+      <c r="C174" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B175" t="s">
+        <v>238</v>
+      </c>
+      <c r="C175" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B176" t="s">
+        <v>239</v>
+      </c>
+      <c r="C176" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B177" t="s">
+        <v>240</v>
+      </c>
+      <c r="C177" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B178" t="s">
+        <v>241</v>
+      </c>
+      <c r="C178" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B179" t="s">
+        <v>242</v>
+      </c>
+      <c r="C179" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B180" t="s">
+        <v>243</v>
+      </c>
+      <c r="C180" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B181" t="s">
+        <v>244</v>
+      </c>
+      <c r="C181" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B182" t="s">
+        <v>245</v>
+      </c>
+      <c r="C182" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B183" t="s">
+        <v>246</v>
+      </c>
+      <c r="C183" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B184" t="s">
+        <v>247</v>
+      </c>
+      <c r="C184" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B185" t="s">
+        <v>248</v>
+      </c>
+      <c r="C185" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B186" t="s">
+        <v>249</v>
+      </c>
+      <c r="C186" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B187" t="s">
+        <v>250</v>
+      </c>
+      <c r="C187" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B188" t="s">
+        <v>251</v>
+      </c>
+      <c r="C188" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B189" t="s">
+        <v>252</v>
+      </c>
+      <c r="C189" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B190" t="s">
+        <v>253</v>
+      </c>
+      <c r="C190" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B191" t="s">
+        <v>254</v>
+      </c>
+      <c r="C191" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B192" t="s">
+        <v>255</v>
+      </c>
+      <c r="C192" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B193" t="s">
+        <v>256</v>
+      </c>
+      <c r="C193" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B194" t="s">
+        <v>257</v>
+      </c>
+      <c r="C194" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B195" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B196" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B197" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B198" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B199" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B200" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B201" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B202" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B203" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B204" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B205" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B206" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B207" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B208" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B209" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B210" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B211" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B212" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B213" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B214" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B215" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B216" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B217" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B218" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B219" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B220" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B221" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B222" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B223" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B224" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B225" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B226" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B227" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B228" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B229" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B230" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B231" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B232" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B233" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B234" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B235" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B236" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B237" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B238" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B239" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B240" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B241" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B242" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B243" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B244" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B245" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B246" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B247" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B248" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B249" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B250" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B251" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B252" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B253" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B254" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B255" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B256" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B257" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B258" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B259" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B260" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B261" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B262" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B263" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B264" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B265" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B266" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B267" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B268" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B269" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B270" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B271" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B272" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B273" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B274" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B275" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B276" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B277" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B278" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B279" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B280" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B281" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B282" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B283" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B284" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B285" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B286" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B287" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B288" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B289" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B290" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B291" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B292" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B293" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B294" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B295" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B296" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B299" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B300" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B301" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B302" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B303" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B304" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B305" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B306" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B307" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B308" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B309" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B310" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B311" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B312" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B313" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B314" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B315" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B316" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>